--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>199800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25291.14</t>
+          <t>269800</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34265.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>25291.14</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>34265.5</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,183 +201,225 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>269800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>34265.5</t>
+          <t>319800</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40594.61</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>34265.5</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>40594.61</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,183 +243,225 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>319800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>40594.61</t>
+          <t>419800</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53415.12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>40594.61</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>53415.12</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,183 +285,225 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>419800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>53415.12</t>
+          <t>499800</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63737.71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>53415.12</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>63737.71</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,183 +327,225 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>499800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>63737.71</t>
+          <t>579800</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74060.29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>63737.71</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>74060.29</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,183 +369,225 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>579800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>74060.29</t>
+          <t>624800</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79829.52</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>74060.29</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>79829.52</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,183 +411,225 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>624800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>79829.52</t>
+          <t>784800</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100608.74</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>79829.52</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>100608.74</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -577,59 +577,86 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>09/29 10:28:07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>784800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100608.74</t>
+          <t>784800</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100608.74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>100608.74</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>79829.74</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,210 +453,252 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>784800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100608.74</t>
+          <t>924800</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>118790.56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>79829.74</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>98011.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -622,83 +622,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>924800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>118790.56</t>
+          <t>924800</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>118790.56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>38960</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>98011.56</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>79830.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,83 +649,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>924800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>118790.56</t>
+          <t>924800</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>38960</t>
+          <t>118790.56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>59739</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>79830.56</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>59051.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,83 +691,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>924800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>118790.56</t>
+          <t>1057800</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>59739</t>
+          <t>135626</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>59739</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>59051.56</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>75887</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,83 +718,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1057800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>1057800</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>59739</t>
+          <t>135626</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>76574</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>75887</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>59052</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -664,7 +664,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,83 +745,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1057800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>1057800</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>76574</t>
+          <t>135626</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>93409</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>59052</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>42217</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,161 +537,176 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>09/09 12:12:36</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>10101.27</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -706,7 +721,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,83 +787,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1057800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>1137800</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93409</t>
+          <t>146015.61</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>93409</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>42217</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>52606.61</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -706,12 +706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,83 +814,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1137800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>146015.61</t>
+          <t>1137800</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93409</t>
+          <t>146015.61</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>103798</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>52606.61</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>42217.61</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/09 12:12:36</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10101.27</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -618,154 +618,184 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>09/11 10:39:47</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8860.76</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>09/09 12:12:36</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>79800</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10101.27</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>代付</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +805,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -829,7 +859,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -841,7 +871,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/29 10:28:07</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -856,7 +886,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -865,59 +895,113 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1137800</t>
-        </is>
-      </c>
-    </row>
+          <t>09/29 10:28:07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>146015.61</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>103798</t>
+          <t>1229426</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>157468.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>103798</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>42217.61</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>53670.86</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11 10:39:47</t>
+          <t>09/11 10:42:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8860.76</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/09 12:12:36</t>
+          <t>09/11 10:39:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10101.27</t>
+          <t>8860.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1229426</t>
+          <t>1249626</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>157468.86</t>
+          <t>160354.61</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>53670.86</t>
+          <t>56556.61</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>09/11 10:42:40</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6329.11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>09/11 10:39:47</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>8860.76</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,7 +859,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -859,7 +874,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -886,7 +901,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,83 +940,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1249626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>160354.61</t>
+          <t>1299626</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>103798</t>
+          <t>166764.86</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>103798</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>56556.61</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>62966.86</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -702,142 +702,127 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>09/11 10:39:47</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>70000</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>8860.76</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -859,7 +844,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -874,7 +859,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -886,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -901,7 +886,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -913,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/29 12:28:49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 10:28:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -955,7 +940,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -964,86 +949,59 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>09/29 10:28:07</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1279626</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1299626</t>
+          <t>164562</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>166764.86</t>
+          <t>103798</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>103798</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>62966.86</t>
+          <t>60764</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -790,12 +790,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -817,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -898,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,83 +925,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1279626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>164562</t>
+          <t>1279626</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>103798</t>
+          <t>164562</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>116785</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>60764</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>47777</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>09/18 10:24:21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6329.11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>09/17 18:20:33</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>8974.36</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -871,7 +886,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -886,7 +901,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -913,7 +928,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -925,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,83 +967,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1279626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>164562</t>
+          <t>1579626</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>116785</t>
+          <t>204035.69</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>116785</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>47777</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>87250.69</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -832,12 +832,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -940,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -967,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,83 +994,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1579626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>204035.69</t>
+          <t>1579626</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>116785</t>
+          <t>204035.69</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>136785</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>87250.69</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>67250.69</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -832,12 +832,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,7 +940,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -967,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1021,83 +1021,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1579626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>204035.69</t>
+          <t>1579626</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>136785</t>
+          <t>204035.69</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>156258</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>67250.69</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>47777.69</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>09/18 10:24:21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6329.11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>09/17 18:20:33</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>8974.36</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -874,7 +889,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,7 +982,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -982,7 +997,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -994,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1009,7 +1024,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1021,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1048,83 +1063,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1579626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>204035.69</t>
+          <t>1629626</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>156258</t>
+          <t>210445.94</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>156258</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>47777.69</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>54187.94</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -874,12 +874,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1036,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,83 +1090,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1629626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>210445.94</t>
+          <t>1629626</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>156258</t>
+          <t>210445.94</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>162668</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>54187.94</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>47777.94</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18 10:24:21</t>
+          <t>09/18 11:56:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>12820.51</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1629626</t>
+          <t>1659626</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>210445.94</t>
+          <t>214458.6</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>47777.94</t>
+          <t>51790.6</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -874,12 +874,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,83 +1117,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1659626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>214458.6</t>
+          <t>1659626</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>162668</t>
+          <t>214458.6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>175655</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>51790.6</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>38803.6</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,166 +747,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>09/18 11:56:15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>12820.51</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>09/18 10:24:21</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -970,7 +985,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -982,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,7 +1078,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1078,7 +1093,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1090,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1105,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1117,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1144,83 +1159,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1659626</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>214458.6</t>
+          <t>1767326</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>227592.74</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>175655</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>38803.6</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>51937.74</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -916,12 +916,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1024,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1132,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,83 +1186,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1767326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>227592.74</t>
+          <t>1767326</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>227592.74</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>188789</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>51937.74</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>38803.74</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -786,142 +786,127 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>09/18 10:24:21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>6329.11</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -943,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1012,7 +997,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1024,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,7 +1090,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1120,7 +1105,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1132,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1147,7 +1132,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1159,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/29 12:28:49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 10:28:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1201,7 +1186,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1210,86 +1195,59 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>09/29 10:28:07</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1777326</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1767326</t>
+          <t>229222.34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>227592.74</t>
+          <t>188789</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>188789</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>38803.74</t>
+          <t>40433.34</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,166 +747,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>09/22 13:49:28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10322.58</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>09/20 17:05:11</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>80000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>7.75</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>10322.58</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -916,7 +931,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -928,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -997,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1009,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1024,7 +1039,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1036,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1105,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1117,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1144,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1159,7 +1174,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1171,7 +1186,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/29 10:28:07</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1186,7 +1201,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1195,59 +1210,113 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1777326</t>
-        </is>
-      </c>
-    </row>
+          <t>09/29 10:28:07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>229222.34</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>188789</t>
+          <t>1877326</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>242209.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>208789</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>40433.34</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>33420.35</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -916,12 +916,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -970,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1213,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1240,83 +1240,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1877326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>242209.35</t>
+          <t>1877326</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>208789</t>
+          <t>242209.35</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>222555</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>33420.35</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>19654.35</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>09/22 13:49:28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10322.58</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>09/20 17:05:11</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>80000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>7.75</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>10322.58</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -985,7 +1000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -997,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1093,7 +1108,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1105,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1159,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,7 +1201,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1201,7 +1216,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1213,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1228,7 +1243,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1240,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1267,83 +1282,110 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1877326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>242209.35</t>
+          <t>2017326</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>222555</t>
+          <t>259282.52</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>222555</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>19654.35</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>36727.52</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -958,12 +958,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -985,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1120,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1255,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1282,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1309,83 +1309,110 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2017326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>259282.52</t>
+          <t>2017326</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>222555</t>
+          <t>259282.52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>239628</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>36727.52</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>19654.52</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/21 14:53:16</t>
+          <t>10/26 10:21:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -828,142 +828,127 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>09/20 17:05:11</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>80000</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>7.75</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>10322.58</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -985,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1027,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1039,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1120,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1147,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1228,7 +1213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1243,7 +1228,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1255,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1270,7 +1255,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1282,12 +1267,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/29 12:28:49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1309,12 +1294,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 10:28:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1324,7 +1309,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1333,86 +1318,59 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>09/29 10:28:07</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2077326</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2017326</t>
+          <t>266137.36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>259282.52</t>
+          <t>239628</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>239628</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>19654.52</t>
+          <t>26509.36</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -916,12 +916,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1024,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1132,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1267,12 +1267,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1294,83 +1294,110 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2077326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>266137.36</t>
+          <t>2077326</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>239628</t>
+          <t>266137.36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>267128</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>26509.36</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-990.64</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 10:21:46</t>
+          <t>10/26 11:54:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>18831.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/21 14:53:16</t>
+          <t>10/26 10:21:46</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>09/29 10:22:56</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20779.22</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>09/28 23:32:07</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>5769.23</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>aoe168188</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -958,7 +973,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -970,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1039,7 +1054,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1051,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1147,7 +1162,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1159,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1213,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1240,7 +1255,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1255,7 +1270,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1267,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1282,7 +1297,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1294,12 +1309,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1321,83 +1336,110 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2077326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>266137.36</t>
+          <t>2222326</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>267128</t>
+          <t>284968.53</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>267128</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>-990.64</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>17840.53</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 11:54:43</t>
+          <t>10/27 13:29:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18831.17</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/26 10:21:46</t>
+          <t>10/26 11:54:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>18831.17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/21 14:53:16</t>
+          <t>10/26 10:21:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>09/29 10:22:56</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20779.22</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>09/28 23:32:07</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>5769.23</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>aoe168188</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1000,7 +1015,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1012,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1039,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1081,7 +1096,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1093,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1120,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1147,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1189,7 +1204,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1201,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1228,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1255,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1282,7 +1297,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1297,7 +1312,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1309,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1324,7 +1339,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1336,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1363,83 +1378,110 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2222326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>284968.53</t>
+          <t>2322326</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>267128</t>
+          <t>297955.54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>267128</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>17840.53</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>30827.54</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -1000,12 +1000,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
+          <t>10/27 14:03:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1054,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1189,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1270,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1324,7 +1324,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1351,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,83 +1405,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2322326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>297955.54</t>
+          <t>2322326</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>267128</t>
+          <t>297955.54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>280115</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>30827.54</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>17840.54</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 13:29:58</t>
+          <t>10/28 13:19:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/26 11:54:43</t>
+          <t>10/28 13:18:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>1300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18831.17</t>
+          <t>158536.59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/26 10:21:46</t>
+          <t>10/27 13:29:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/21 14:53:16</t>
+          <t>10/26 11:54:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>18831.17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/26 10:21:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -912,154 +912,184 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>09/29 10:22:56</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20779.22</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>09/28 23:32:07</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>5769.23</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>aoe168188</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>代付</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/27 14:03:24</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>12987</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/28 14:30:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/27 14:03:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1108,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1123,7 +1153,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1135,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1150,7 +1180,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1162,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1177,7 +1207,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1189,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1204,7 +1234,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1216,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1258,7 +1288,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1270,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1285,7 +1315,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1297,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1312,7 +1342,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1324,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1351,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1366,7 +1396,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1378,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1432,83 +1462,164 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/29 10:28:07</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>16835</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>09/29 12:29:09</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>09/29 10:28:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2322326</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>297955.54</t>
-        </is>
-      </c>
-    </row>
+          <t>20779</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>280115</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3752326</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>472345.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>295968</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>17840.54</t>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>176377.79</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/28 13:19:13</t>
+          <t>10/28 15:04:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>136000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>17662.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/28 13:18:18</t>
+          <t>10/28 13:19:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1300000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>158536.59</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/27 13:29:58</t>
+          <t>10/28 13:18:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>158536.59</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/26 11:54:43</t>
+          <t>10/27 13:29:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18831.17</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/26 10:21:46</t>
+          <t>10/26 11:54:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>18831.17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/21 14:53:16</t>
+          <t>10/26 10:21:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/29 10:22:56</t>
+          <t>09/29 12:01:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>09/29 10:22:56</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20779.22</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>09/28 23:32:07</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>5769.23</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>aoe168188</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/28 14:30:51</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/27 14:03:24</t>
+          <t>10/28 14:30:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
+          <t>10/27 14:03:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1153,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1165,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1180,7 +1195,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1192,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1246,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1261,7 +1276,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1273,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1300,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1369,7 +1384,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1381,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1408,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1462,7 +1477,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
+          <t>09/30 19:09:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1477,7 +1492,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1489,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1504,7 +1519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,83 +1558,110 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>3752326</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>472345.79</t>
+          <t>3888326</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>295968</t>
+          <t>490008.12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>295968</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>176377.79</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>194040.12</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/28 15:04:59</t>
+          <t>10/31 11:18:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>136000</t>
+          <t>157700</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17662.34</t>
+          <t>19231.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/28 13:19:13</t>
+          <t>10/28 15:04:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>136000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>17662.34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/28 13:18:18</t>
+          <t>10/28 13:19:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1300000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>158536.59</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/27 13:29:58</t>
+          <t>10/28 13:18:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>158536.59</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/26 11:54:43</t>
+          <t>10/27 13:29:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18831.17</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/26 10:21:46</t>
+          <t>10/26 11:54:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>18831.17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/21 14:53:16</t>
+          <t>10/26 10:21:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/20 13:50:02</t>
+          <t>10/20 14:16:14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/19 11:12:13</t>
+          <t>10/19 14:36:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>13134.15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/08 13:57:29</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/08 13:57:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -954,184 +954,154 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>09/29 10:22:56</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>20779.22</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>45000</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>5769.23</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>aoe168188</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
           <t>代付</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>10/28 16:19:42</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>17662</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/28 14:30:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/28 14:30:51</t>
+          <t>10/27 14:03:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1153,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/27 14:03:24</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1138,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1195,7 +1165,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1207,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1276,7 +1246,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1288,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1315,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1342,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1369,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1384,7 +1354,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1396,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/07 21:28:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1450,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1465,7 +1435,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1474,194 +1444,59 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>09/30 19:09:04</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>16835</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/30 19:01:32</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>16835</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t/>
+          <t>3701026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18181</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t/>
+          <t>464509.56</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/29 10:28:07</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>3888326</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>490008.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>295968</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+          <t>237056</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>194040.12</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>227453.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-all.xlsx
@@ -1042,12 +1042,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/28 16:19:42</t>
+          <t>10/31 11:19:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1069,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/28 14:30:51</t>
+          <t>10/28 16:19:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/27 14:03:24</t>
+          <t>10/28 14:30:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
+          <t>10/27 14:03:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/21 15:34:08</t>
+          <t>10/26 10:40:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
+          <t>10/21 15:34:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>10/20 15:07:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
+          <t>10/20 14:16:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1258,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>10/19 15:38:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1285,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/17 10:20:01</t>
+          <t>10/19 11:36:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/16 12:56:10</t>
+          <t>10/17 10:20:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
+          <t>10/16 12:56:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/13 14:02:36</t>
+          <t>10/16 12:34:05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/07 21:28:34</t>
+          <t>10/13 14:02:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1420,83 +1420,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>10/07 21:28:34</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>09/30 19:01:32</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>16835</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3701026</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>464509.56</t>
+          <t>3701026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>237056</t>
+          <t>464509.56</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>237744</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>227453.56</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>226765.56</t>
         </is>
       </c>
     </row>
